--- a/static/pdf/DECLARATION_JUIN_2026.xlsx
+++ b/static/pdf/DECLARATION_JUIN_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Déclaration" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Déclaration" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -581,43 +581,43 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1100</v>
+        <v>27500</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>209</v>
+        <v>5225</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1309</v>
+        <v>32725</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>FA00004</t>
+          <t>FA00003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Commerce Delta</t>
+          <t>Entreprise Gamma</t>
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2400</v>
+        <v>33750</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>456</v>
+        <v>6412.5</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>2856</v>
+        <v>40162.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -631,37 +631,37 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1200</v>
+        <v>30000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>228</v>
+        <v>5700</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1428</v>
+        <v>35700</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>FA00005</t>
+          <t>FA00004</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Societe Epsilon</t>
+          <t>Commerce Delta</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>500</v>
+        <v>60000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>95</v>
+        <v>11400</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>595</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="7">
@@ -673,141 +673,63 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="7" t="n">
-        <v>2300</v>
+        <v>57500</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>437</v>
+        <v>10925</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2737</v>
+        <v>68425</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>FA260625235041</t>
+          <t>FA00005</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Societe Alpha</t>
+          <t>Societe Epsilon</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>750</v>
+        <v>12500</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>142.5</v>
+        <v>2375</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>892.5</v>
+        <v>14875</v>
       </c>
     </row>
     <row r="8">
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>FA260630175732</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Societe Alpha</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>FA260630183142</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Societe Alpha</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>228</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>FA260630191817</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Societe Alpha</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>228</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="7" t="n">
-        <v>6550</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>1244.5</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>7794.5</v>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="7" t="n">
+        <v>106250</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>20187.5</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>126437.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H8:J8"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="H11:J11"/>
     <mergeCell ref="H3:M3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/pdf/DECLARATION_JUIN_2026.xlsx
+++ b/static/pdf/DECLARATION_JUIN_2026.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,6 +99,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,30 +581,82 @@
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>BL82455FC</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Carat S.a.r.l</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>1274.49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>BLCDFCD7A</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Carat S.a.r.l</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1274.49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0</v>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>406.98</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>2548.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="H5:J5"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="H3:M3"/>
+    <mergeCell ref="H7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
